--- a/public/payroll-template.xlsx
+++ b/public/payroll-template.xlsx
@@ -12,9 +12,9 @@
     <sheet sheetId="149" name="3월" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1월'!$A1:$F25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2월'!$A1:$F25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'3월'!$A1:$F25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1월'!$A1:$F30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2월'!$A1:$F30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'3월'!$A1:$F30</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
@@ -23,358 +23,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="5">
   <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>급여내역</t>
-    </r>
+    <t>급여내역</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-      </rPr>
-      <t>원천징수공제내역</t>
-    </r>
+    <t>원천징수공제내역</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">     : </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>비과세</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>항목에</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> 8</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>세이하</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>자녀</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>육아수당</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>반영</t>
-    </r>
+    <t xml:space="preserve">     : 비과세 항목에 8세이하 자녀 육아수당 반영</t>
   </si>
   <si>
-    <r>
-      <t>2. 2017</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>년</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>건강보험료</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>확정분</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">(3.06%) </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>반영</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>_2016</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>년</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>보수총액</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>신고액</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>기준</t>
-    </r>
+    <t>2. 2017년 건강보험료 확정분(3.06%) 반영_2016년 보수총액 신고액 기준</t>
   </si>
   <si>
-    <r>
-      <t>3. 2016</t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>년</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>국민연금보험료</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>확정</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <charset val="129"/>
-        <color indexed="60"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-      </rPr>
-      <t>적용</t>
-    </r>
+    <t>3. 2016년 국민연금보험료 확정 적용</t>
   </si>
 </sst>
 </file>
@@ -612,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -674,9 +335,6 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -701,6 +359,9 @@
     <xf numFmtId="165" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -724,9 +385,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1115,7 +773,14 @@
     <col min="9" max="16384" width="9.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="45" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
     <row r="2" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
@@ -1153,190 +818,225 @@
       <c r="B6" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="21"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="20"/>
       <c r="F6" s="13"/>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="26"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="26"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="26"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="27"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="26"/>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="26"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="27"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="26"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="27"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="26"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="27"/>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="27"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="27"/>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39"/>
-      <c r="B20" s="36" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="26"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="26"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="26"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="26"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="21"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="26"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="26"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="26"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="26"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
+      <c r="B25" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="40"/>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="41" t="s">
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="39"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="37"/>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="36" t="s">
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="37"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="37"/>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="46"/>
-    </row>
-    <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="37"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="37"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="42"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="45"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5905511811023623" right="0.5905511811023623" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
@@ -1363,7 +1063,14 @@
     <col min="9" max="16384" width="9.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="45" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
     <row r="2" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
@@ -1401,190 +1108,225 @@
       <c r="B6" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="21"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="20"/>
       <c r="F6" s="13"/>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="26"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="26"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="26"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="27"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="26"/>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="26"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="27"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="26"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="27"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="26"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="27"/>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="27"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="27"/>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39"/>
-      <c r="B20" s="36" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="26"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="26"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="26"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="26"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="21"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="26"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="26"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="26"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="26"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
+      <c r="B25" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="40"/>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="41" t="s">
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="39"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="37"/>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="36" t="s">
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="37"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="37"/>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="46"/>
-    </row>
-    <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="37"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="37"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="42"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="45"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5905511811023623" right="0.5905511811023623" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
@@ -1611,7 +1353,14 @@
     <col min="9" max="16384" width="9.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="45" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
     <row r="2" ht="48" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
@@ -1649,190 +1398,225 @@
       <c r="B6" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="21"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="20"/>
       <c r="F6" s="13"/>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="26"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="26"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="26"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="27"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="26"/>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="26"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="25"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="27"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="26"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="27"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="26"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="27"/>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="27"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="27"/>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
-    </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39"/>
-      <c r="B20" s="36" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="26"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="26"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="26"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="26"/>
+    </row>
+    <row r="20" ht="18.75" customHeight="1" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="21"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="26"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="26"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="26"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="26"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
+      <c r="B25" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="40"/>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="41" t="s">
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="39"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="37"/>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="36" t="s">
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="37"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
-    </row>
-    <row r="23" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="37"/>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="46"/>
-    </row>
-    <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="20" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="37"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="37"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="42"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="45"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5905511811023623" right="0.5905511811023623" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
